--- a/docs/Cottage Rummy Data File.xlsx
+++ b/docs/Cottage Rummy Data File.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomku\Dropbox\Personal\Cottage Rummy Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717F1250-6CDB-4136-B6CC-EE7420AB2EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0119320B-37D2-4C85-856F-D8D46CE937A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="540" yWindow="-15720" windowWidth="27915" windowHeight="14385" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-1009]d/mmm/yy;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -121,14 +121,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -478,12 +478,12 @@
   <dimension ref="A1:AKI268"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -510,7 +510,7 @@
       <c r="J1" s="3"/>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>44580</v>
       </c>
       <c r="B2" s="4">
@@ -531,7 +531,7 @@
       <c r="J2"/>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>44580</v>
       </c>
       <c r="B3" s="4"/>
@@ -552,7 +552,7 @@
       <c r="J3"/>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>44580</v>
       </c>
       <c r="B4" s="4"/>
@@ -573,7 +573,7 @@
       <c r="J4"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+      <c r="A5" s="7">
         <v>44617</v>
       </c>
       <c r="B5">
@@ -593,7 +593,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+      <c r="A6" s="7">
         <v>44618</v>
       </c>
       <c r="C6">
@@ -616,7 +616,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+      <c r="A7" s="7">
         <v>44627</v>
       </c>
       <c r="C7">
@@ -633,7 +633,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+      <c r="A8" s="7">
         <v>44632</v>
       </c>
       <c r="B8">
@@ -659,7 +659,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+      <c r="A9" s="7">
         <v>44635</v>
       </c>
       <c r="B9">
@@ -685,7 +685,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+      <c r="A10" s="7">
         <v>44636</v>
       </c>
       <c r="B10">
@@ -711,7 +711,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
+      <c r="A11" s="7">
         <v>44637</v>
       </c>
       <c r="B11">
@@ -737,7 +737,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
+      <c r="A12" s="7">
         <v>44666</v>
       </c>
       <c r="C12">
@@ -760,7 +760,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
+      <c r="A13" s="7">
         <v>44667</v>
       </c>
       <c r="B13">
@@ -786,7 +786,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
+      <c r="A14" s="7">
         <v>44681</v>
       </c>
       <c r="B14">
@@ -809,7 +809,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
+      <c r="A15" s="7">
         <v>44688</v>
       </c>
       <c r="C15">
@@ -829,7 +829,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="5">
+      <c r="A16" s="7">
         <v>44695</v>
       </c>
       <c r="E16">
@@ -846,7 +846,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
+      <c r="A17" s="7">
         <v>44842</v>
       </c>
       <c r="B17">
@@ -866,7 +866,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="5">
+      <c r="A18" s="7">
         <v>44849</v>
       </c>
       <c r="C18">
@@ -886,7 +886,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
+      <c r="A19" s="7">
         <v>44877</v>
       </c>
       <c r="C19">
@@ -906,7 +906,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="5">
+      <c r="A20" s="7">
         <v>44884</v>
       </c>
       <c r="B20">
@@ -923,7 +923,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
+      <c r="A21" s="7">
         <v>44884</v>
       </c>
       <c r="B21">
@@ -940,7 +940,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
+      <c r="A22" s="7">
         <v>44905</v>
       </c>
       <c r="B22">
@@ -957,7 +957,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
+      <c r="A23" s="7">
         <v>44919</v>
       </c>
       <c r="B23">
@@ -983,7 +983,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="5">
+      <c r="A24" s="7">
         <v>44920</v>
       </c>
       <c r="B24">
@@ -1009,7 +1009,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="5">
+      <c r="A25" s="7">
         <v>44921</v>
       </c>
       <c r="B25">
@@ -1035,7 +1035,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="5">
+      <c r="A26" s="7">
         <v>44923</v>
       </c>
       <c r="B26">
@@ -1055,7 +1055,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="5">
+      <c r="A27" s="7">
         <v>44924</v>
       </c>
       <c r="B27">
@@ -1081,7 +1081,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="5">
+      <c r="A28" s="7">
         <v>44925</v>
       </c>
       <c r="B28">
@@ -1107,7 +1107,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="5">
+      <c r="A29" s="7">
         <v>44926</v>
       </c>
       <c r="C29">
@@ -1130,7 +1130,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="5">
+      <c r="A30" s="7">
         <v>44926</v>
       </c>
       <c r="C30">
@@ -1153,7 +1153,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="5">
+      <c r="A31" s="7">
         <v>44927</v>
       </c>
       <c r="B31">
@@ -1179,7 +1179,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="5">
+      <c r="A32" s="7">
         <v>44927</v>
       </c>
       <c r="C32">
@@ -1196,7 +1196,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="5">
+      <c r="A33" s="7">
         <v>44947</v>
       </c>
       <c r="B33">
@@ -1219,7 +1219,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="5">
+      <c r="A34" s="7">
         <v>44947</v>
       </c>
       <c r="B34">
@@ -1239,7 +1239,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="5">
+      <c r="A35" s="7">
         <v>44952</v>
       </c>
       <c r="E35">
@@ -1256,7 +1256,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="5">
+      <c r="A36" s="7">
         <v>44952</v>
       </c>
       <c r="E36">
@@ -1273,7 +1273,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="5">
+      <c r="A37" s="7">
         <v>44953</v>
       </c>
       <c r="E37">
@@ -1290,7 +1290,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="5">
+      <c r="A38" s="7">
         <v>44953</v>
       </c>
       <c r="E38">
@@ -1307,7 +1307,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="5">
+      <c r="A39" s="7">
         <v>44957</v>
       </c>
       <c r="E39">
@@ -1324,7 +1324,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="5">
+      <c r="A40" s="7">
         <v>44958</v>
       </c>
       <c r="E40">
@@ -1341,7 +1341,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="5">
+      <c r="A41" s="7">
         <v>44959</v>
       </c>
       <c r="E41">
@@ -1358,7 +1358,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="5">
+      <c r="A42" s="7">
         <v>44959</v>
       </c>
       <c r="E42">
@@ -1375,7 +1375,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="5">
+      <c r="A43" s="7">
         <v>44960</v>
       </c>
       <c r="E43">
@@ -1392,7 +1392,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="5">
+      <c r="A44" s="7">
         <v>44961</v>
       </c>
       <c r="E44">
@@ -1409,7 +1409,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="5">
+      <c r="A45" s="7">
         <v>44961</v>
       </c>
       <c r="E45">
@@ -1426,7 +1426,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="5">
+      <c r="A46" s="7">
         <v>44962</v>
       </c>
       <c r="E46">
@@ -1443,7 +1443,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="5">
+      <c r="A47" s="7">
         <v>44996</v>
       </c>
       <c r="B47">
@@ -1469,7 +1469,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="5">
+      <c r="A48" s="7">
         <v>44982</v>
       </c>
       <c r="B48">
@@ -1486,7 +1486,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="5">
+      <c r="A49" s="7">
         <v>44982</v>
       </c>
       <c r="B49">
@@ -1503,7 +1503,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="5">
+      <c r="A50" s="7">
         <v>44982</v>
       </c>
       <c r="B50">
@@ -1520,7 +1520,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="5">
+      <c r="A51" s="7">
         <v>44989</v>
       </c>
       <c r="C51">
@@ -1534,7 +1534,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="5">
+      <c r="A52" s="7">
         <v>44989</v>
       </c>
       <c r="C52">
@@ -1548,7 +1548,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="5">
+      <c r="A53" s="7">
         <v>44989</v>
       </c>
       <c r="C53">
@@ -1562,7 +1562,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="5">
+      <c r="A54" s="7">
         <v>44996</v>
       </c>
       <c r="B54">
@@ -1588,7 +1588,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="5">
+      <c r="A55" s="7">
         <v>44996</v>
       </c>
       <c r="B55">
@@ -1614,7 +1614,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="5">
+      <c r="A56" s="7">
         <v>44998</v>
       </c>
       <c r="B56">
@@ -1640,7 +1640,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="5">
+      <c r="A57" s="7">
         <v>44999</v>
       </c>
       <c r="B57">
@@ -1663,7 +1663,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="5">
+      <c r="A58" s="7">
         <v>45010</v>
       </c>
       <c r="B58">
@@ -1680,7 +1680,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="5">
+      <c r="A59" s="7">
         <v>45017</v>
       </c>
       <c r="B59">
@@ -1697,7 +1697,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="5">
+      <c r="A60" s="7">
         <v>45017</v>
       </c>
       <c r="B60">
@@ -1714,7 +1714,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="5">
+      <c r="A61" s="7">
         <v>45038</v>
       </c>
       <c r="E61">
@@ -1731,7 +1731,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="5">
+      <c r="A62" s="7">
         <v>45045</v>
       </c>
       <c r="B62">
@@ -1754,7 +1754,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="5">
+      <c r="A63" s="7">
         <v>45052</v>
       </c>
       <c r="C63">
@@ -1774,7 +1774,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="5">
+      <c r="A64" s="7">
         <v>45066</v>
       </c>
       <c r="B64">
@@ -1800,7 +1800,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="5">
+      <c r="A65" s="7">
         <v>45067</v>
       </c>
       <c r="B65">
@@ -1820,7 +1820,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="5">
+      <c r="A66" s="7">
         <v>45068</v>
       </c>
       <c r="B66">
@@ -1840,7 +1840,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="5">
+      <c r="A67" s="7">
         <v>45094</v>
       </c>
       <c r="C67">
@@ -1863,7 +1863,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="5">
+      <c r="A68" s="7">
         <v>45101</v>
       </c>
       <c r="C68">
@@ -1883,7 +1883,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="5">
+      <c r="A69" s="7">
         <v>45101</v>
       </c>
       <c r="C69">
@@ -1903,7 +1903,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="5">
+      <c r="A70" s="7">
         <v>45115</v>
       </c>
       <c r="E70">
@@ -1920,7 +1920,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="5">
+      <c r="A71" s="7">
         <v>45115</v>
       </c>
       <c r="E71">
@@ -1937,7 +1937,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="5">
+      <c r="A72" s="7">
         <v>45122</v>
       </c>
       <c r="B72">
@@ -1957,7 +1957,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="5">
+      <c r="A73" s="7">
         <v>45129</v>
       </c>
       <c r="C73">
@@ -1980,7 +1980,7 @@
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="5">
+      <c r="A74" s="7">
         <v>45129</v>
       </c>
       <c r="C74">
@@ -2003,7 +2003,7 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="5">
+      <c r="A75" s="7">
         <v>45136</v>
       </c>
       <c r="E75">
@@ -2020,7 +2020,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="5">
+      <c r="A76" s="7">
         <v>45144</v>
       </c>
       <c r="D76">
@@ -2040,7 +2040,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="5">
+      <c r="A77" s="7">
         <v>45150</v>
       </c>
       <c r="C77">
@@ -2063,7 +2063,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="5">
+      <c r="A78" s="7">
         <v>45151</v>
       </c>
       <c r="C78">
@@ -2086,7 +2086,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="5">
+      <c r="A79" s="7">
         <v>45157</v>
       </c>
       <c r="B79">
@@ -2106,7 +2106,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="5">
+      <c r="A80" s="7">
         <v>45178</v>
       </c>
       <c r="B80">
@@ -2126,7 +2126,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="5">
+      <c r="A81" s="7">
         <v>45179</v>
       </c>
       <c r="C81">
@@ -2146,7 +2146,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="5">
+      <c r="A82" s="7">
         <v>45213</v>
       </c>
       <c r="B82">
@@ -2169,7 +2169,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="5">
+      <c r="A83" s="7">
         <v>45213</v>
       </c>
       <c r="C83">
@@ -2189,7 +2189,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="5">
+      <c r="A84" s="7">
         <v>45227</v>
       </c>
       <c r="C84">
@@ -2209,7 +2209,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="5">
+      <c r="A85" s="7">
         <v>45248</v>
       </c>
       <c r="B85">
@@ -2226,7 +2226,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="5">
+      <c r="A86" s="7">
         <v>45255</v>
       </c>
       <c r="B86">
@@ -2243,7 +2243,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="5">
+      <c r="A87" s="7">
         <v>45255</v>
       </c>
       <c r="B87">
@@ -2260,7 +2260,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="5">
+      <c r="A88" s="7">
         <v>45263</v>
       </c>
       <c r="B88">
@@ -2277,7 +2277,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="5">
+      <c r="A89" s="7">
         <v>45263</v>
       </c>
       <c r="B89">
@@ -2294,7 +2294,7 @@
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="5">
+      <c r="A90" s="7">
         <v>45269</v>
       </c>
       <c r="B90">
@@ -2311,7 +2311,7 @@
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="5">
+      <c r="A91" s="7">
         <v>45269</v>
       </c>
       <c r="B91">
@@ -2328,7 +2328,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="5">
+      <c r="A92" s="7">
         <v>45269</v>
       </c>
       <c r="B92">
@@ -2345,7 +2345,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="5">
+      <c r="A93" s="7">
         <v>45283</v>
       </c>
       <c r="E93">
@@ -2362,7 +2362,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="5">
+      <c r="A94" s="7">
         <v>45283</v>
       </c>
       <c r="E94">
@@ -2379,7 +2379,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="5">
+      <c r="A95" s="7">
         <v>45283</v>
       </c>
       <c r="E95">
@@ -2396,7 +2396,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="5">
+      <c r="A96" s="7">
         <v>45284</v>
       </c>
       <c r="B96">
@@ -2422,7 +2422,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="5">
+      <c r="A97" s="7">
         <v>45285</v>
       </c>
       <c r="B97">
@@ -2448,7 +2448,7 @@
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="5">
+      <c r="A98" s="7">
         <v>45285</v>
       </c>
       <c r="B98">
@@ -2474,7 +2474,7 @@
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="5">
+      <c r="A99" s="7">
         <v>45286</v>
       </c>
       <c r="C99">
@@ -2494,7 +2494,7 @@
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="5">
+      <c r="A100" s="7">
         <v>45286</v>
       </c>
       <c r="B100">
@@ -2520,7 +2520,7 @@
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="5">
+      <c r="A101" s="7">
         <v>45290</v>
       </c>
       <c r="B101">
@@ -2546,7 +2546,7 @@
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="5">
+      <c r="A102" s="7">
         <v>45291</v>
       </c>
       <c r="C102">
@@ -2566,7 +2566,7 @@
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="5">
+      <c r="A103" s="7">
         <v>45297</v>
       </c>
       <c r="B103">
@@ -2589,7 +2589,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="5">
+      <c r="A104" s="7">
         <v>45297</v>
       </c>
       <c r="B104">
@@ -2612,7 +2612,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="5">
+      <c r="A105" s="7">
         <v>45304</v>
       </c>
       <c r="B105">
@@ -2632,7 +2632,7 @@
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="5">
+      <c r="A106" s="7">
         <v>45304</v>
       </c>
       <c r="B106">
@@ -2655,7 +2655,7 @@
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="5">
+      <c r="A107" s="7">
         <v>45318</v>
       </c>
       <c r="B107">
@@ -2672,7 +2672,7 @@
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="5">
+      <c r="A108" s="7">
         <v>45318</v>
       </c>
       <c r="B108">
@@ -2689,7 +2689,7 @@
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="5">
+      <c r="A109" s="7">
         <v>45325</v>
       </c>
       <c r="B109">
@@ -2706,7 +2706,7 @@
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="5">
+      <c r="A110" s="7">
         <v>45325</v>
       </c>
       <c r="B110">
@@ -2723,7 +2723,7 @@
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="5">
+      <c r="A111" s="7">
         <v>45346</v>
       </c>
       <c r="B111">
@@ -2740,7 +2740,7 @@
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="5">
+      <c r="A112" s="7">
         <v>45346</v>
       </c>
       <c r="B112">
@@ -2757,7 +2757,7 @@
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="5">
+      <c r="A113" s="7">
         <v>45356</v>
       </c>
       <c r="C113">
@@ -2780,7 +2780,7 @@
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="5">
+      <c r="A114" s="7">
         <v>45357</v>
       </c>
       <c r="C114">
@@ -2800,7 +2800,7 @@
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="5">
+      <c r="A115" s="7">
         <v>45358</v>
       </c>
       <c r="C115">
@@ -2820,7 +2820,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="5">
+      <c r="A116" s="7">
         <v>45358</v>
       </c>
       <c r="C116">
@@ -2840,7 +2840,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="5">
+      <c r="A117" s="7">
         <v>45374</v>
       </c>
       <c r="B117">
@@ -2857,7 +2857,7 @@
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="5">
+      <c r="A118" s="7">
         <v>45374</v>
       </c>
       <c r="B118">
@@ -2874,7 +2874,7 @@
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="5">
+      <c r="A119" s="7">
         <v>45388</v>
       </c>
       <c r="B119">
@@ -2891,7 +2891,7 @@
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="5">
+      <c r="A120" s="7">
         <v>45402</v>
       </c>
       <c r="C120">
@@ -2911,7 +2911,7 @@
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="5">
+      <c r="A121" s="7">
         <v>45409</v>
       </c>
       <c r="B121">
@@ -2928,7 +2928,7 @@
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A122" s="5">
+      <c r="A122" s="7">
         <v>45416</v>
       </c>
       <c r="C122">
@@ -2948,7 +2948,7 @@
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" s="5">
+      <c r="A123" s="7">
         <v>45416</v>
       </c>
       <c r="C123">
@@ -2968,7 +2968,7 @@
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="5">
+      <c r="A124" s="7">
         <v>45423</v>
       </c>
       <c r="E124">
@@ -2985,7 +2985,7 @@
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="5">
+      <c r="A125" s="7">
         <v>45423</v>
       </c>
       <c r="E125">
@@ -3002,7 +3002,7 @@
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="5">
+      <c r="A126" s="7">
         <v>45437</v>
       </c>
       <c r="C126">
@@ -3022,7 +3022,7 @@
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" s="5">
+      <c r="A127" s="7">
         <v>45437</v>
       </c>
       <c r="C127">
@@ -3042,7 +3042,7 @@
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" s="5">
+      <c r="A128" s="7">
         <v>45444</v>
       </c>
       <c r="C128">
@@ -3062,7 +3062,7 @@
       </c>
     </row>
     <row r="129" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A129" s="5">
+      <c r="A129" s="7">
         <v>45451</v>
       </c>
       <c r="E129">
@@ -3079,7 +3079,7 @@
       </c>
     </row>
     <row r="130" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A130" s="5">
+      <c r="A130" s="7">
         <v>45465</v>
       </c>
       <c r="E130">
@@ -3096,7 +3096,7 @@
       </c>
     </row>
     <row r="131" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A131" s="5">
+      <c r="A131" s="7">
         <v>45501</v>
       </c>
       <c r="C131">
@@ -3116,7 +3116,7 @@
       </c>
     </row>
     <row r="132" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A132" s="5">
+      <c r="A132" s="7">
         <v>45507</v>
       </c>
       <c r="C132">
@@ -3136,7 +3136,7 @@
       </c>
     </row>
     <row r="133" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A133" s="5">
+      <c r="A133" s="7">
         <v>45559</v>
       </c>
       <c r="C133">
@@ -3278,7 +3278,7 @@
       <c r="AKI133" s="1"/>
     </row>
     <row r="134" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A134" s="5">
+      <c r="A134" s="7">
         <v>45514</v>
       </c>
       <c r="E134">
@@ -3295,7 +3295,7 @@
       </c>
     </row>
     <row r="135" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A135" s="5">
+      <c r="A135" s="7">
         <v>45521</v>
       </c>
       <c r="B135">
@@ -3312,7 +3312,7 @@
       </c>
     </row>
     <row r="136" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A136" s="5">
+      <c r="A136" s="7">
         <v>45559</v>
       </c>
       <c r="C136">
@@ -3332,7 +3332,7 @@
       </c>
     </row>
     <row r="137" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A137" s="5">
+      <c r="A137" s="7">
         <v>45535</v>
       </c>
       <c r="B137">
@@ -3349,7 +3349,7 @@
       </c>
     </row>
     <row r="138" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A138" s="5">
+      <c r="A138" s="7">
         <v>45542</v>
       </c>
       <c r="E138">
@@ -3366,7 +3366,7 @@
       </c>
     </row>
     <row r="139" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A139" s="5">
+      <c r="A139" s="7">
         <v>45550</v>
       </c>
       <c r="E139">
@@ -3383,7 +3383,7 @@
       </c>
     </row>
     <row r="140" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A140" s="5">
+      <c r="A140" s="7">
         <v>45556</v>
       </c>
       <c r="B140">
@@ -3400,7 +3400,7 @@
       </c>
     </row>
     <row r="141" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A141" s="5">
+      <c r="A141" s="7">
         <v>45563</v>
       </c>
       <c r="C141">
@@ -3420,7 +3420,7 @@
       </c>
     </row>
     <row r="142" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A142" s="5">
+      <c r="A142" s="7">
         <v>45570</v>
       </c>
       <c r="E142">
@@ -3437,7 +3437,7 @@
       </c>
     </row>
     <row r="143" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A143" s="5">
+      <c r="A143" s="7">
         <v>45570</v>
       </c>
       <c r="E143">
@@ -3454,7 +3454,7 @@
       </c>
     </row>
     <row r="144" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A144" s="5">
+      <c r="A144" s="7">
         <v>45570</v>
       </c>
       <c r="E144">
@@ -3471,7 +3471,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A145" s="5">
+      <c r="A145" s="7">
         <v>45577</v>
       </c>
       <c r="E145">
@@ -3488,7 +3488,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A146" s="5">
+      <c r="A146" s="7">
         <v>45591</v>
       </c>
       <c r="E146">
@@ -3505,7 +3505,7 @@
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A147" s="5">
+      <c r="A147" s="7">
         <v>45619</v>
       </c>
       <c r="B147">
@@ -3522,7 +3522,7 @@
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A148" s="5">
+      <c r="A148" s="7">
         <v>45631</v>
       </c>
       <c r="B148">
@@ -3539,7 +3539,7 @@
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A149" s="5">
+      <c r="A149" s="7">
         <v>45647</v>
       </c>
       <c r="C149">
@@ -3559,7 +3559,7 @@
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A150" s="5">
+      <c r="A150" s="7">
         <v>45647</v>
       </c>
       <c r="E150">
@@ -3576,7 +3576,7 @@
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A151" s="5">
+      <c r="A151" s="7">
         <v>45650</v>
       </c>
       <c r="B151">
@@ -3599,7 +3599,7 @@
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A152" s="5">
+      <c r="A152" s="7">
         <v>45650</v>
       </c>
       <c r="C152">
@@ -3619,7 +3619,7 @@
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A153" s="5">
+      <c r="A153" s="7">
         <v>45651</v>
       </c>
       <c r="B153">
@@ -3642,7 +3642,7 @@
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A154" s="5">
+      <c r="A154" s="7">
         <v>45651</v>
       </c>
       <c r="C154">
@@ -3662,7 +3662,7 @@
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A155" s="5">
+      <c r="A155" s="7">
         <v>45652</v>
       </c>
       <c r="B155">
@@ -3685,7 +3685,7 @@
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A156" s="5">
+      <c r="A156" s="7">
         <v>45652</v>
       </c>
       <c r="C156">
@@ -3705,7 +3705,7 @@
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A157" s="5">
+      <c r="A157" s="7">
         <v>45654</v>
       </c>
       <c r="B157">
@@ -3731,7 +3731,7 @@
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A158" s="5">
+      <c r="A158" s="7">
         <v>45654</v>
       </c>
       <c r="C158">
@@ -3754,7 +3754,7 @@
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A159" s="5">
+      <c r="A159" s="7">
         <v>45655</v>
       </c>
       <c r="B159">
@@ -3774,7 +3774,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A160" s="5">
+      <c r="A160" s="7">
         <v>45657</v>
       </c>
       <c r="C160">
@@ -3797,7 +3797,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A161" s="5">
+      <c r="A161" s="7">
         <v>45657</v>
       </c>
       <c r="C161">
@@ -3820,7 +3820,7 @@
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A162" s="5">
+      <c r="A162" s="7">
         <v>45658</v>
       </c>
       <c r="B162">
@@ -3846,7 +3846,7 @@
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A163" s="5">
+      <c r="A163" s="7">
         <v>45661</v>
       </c>
       <c r="B163">
@@ -3872,7 +3872,7 @@
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A164" s="5">
+      <c r="A164" s="7">
         <v>45668</v>
       </c>
       <c r="B164">
@@ -3886,7 +3886,7 @@
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A165" s="5">
+      <c r="A165" s="7">
         <v>45675</v>
       </c>
       <c r="B165">
@@ -3903,7 +3903,7 @@
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A166" s="5">
+      <c r="A166" s="7">
         <v>45675</v>
       </c>
       <c r="C166">
@@ -3917,7 +3917,7 @@
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A167" s="5">
+      <c r="A167" s="7">
         <v>45682</v>
       </c>
       <c r="B167">
@@ -3934,7 +3934,7 @@
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A168" s="5">
+      <c r="A168" s="7">
         <v>45682</v>
       </c>
       <c r="C168">
@@ -3948,7 +3948,7 @@
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A169" s="5">
+      <c r="A169" s="7">
         <v>45689</v>
       </c>
       <c r="B169">
@@ -3968,7 +3968,7 @@
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A170" s="5">
+      <c r="A170" s="7">
         <v>45696</v>
       </c>
       <c r="C170">
@@ -3982,7 +3982,7 @@
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A171" s="5">
+      <c r="A171" s="7">
         <v>45696</v>
       </c>
       <c r="C171">
@@ -3996,7 +3996,7 @@
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A172" s="5">
+      <c r="A172" s="7">
         <v>45696</v>
       </c>
       <c r="C172">
@@ -4010,7 +4010,7 @@
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A173" s="5">
+      <c r="A173" s="7">
         <v>45705</v>
       </c>
       <c r="C173">
@@ -4024,7 +4024,7 @@
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A174" s="5">
+      <c r="A174" s="7">
         <v>45737</v>
       </c>
       <c r="E174">
@@ -4041,7 +4041,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A175" s="5">
+      <c r="A175" s="7">
         <v>45740</v>
       </c>
       <c r="E175">
@@ -4058,7 +4058,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A176" s="5">
+      <c r="A176" s="7">
         <v>45746</v>
       </c>
       <c r="E176">
@@ -4075,7 +4075,7 @@
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A177" s="5">
+      <c r="A177" s="7">
         <v>45752</v>
       </c>
       <c r="B177">
@@ -4095,7 +4095,7 @@
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A178" s="5">
+      <c r="A178" s="7">
         <v>45752</v>
       </c>
       <c r="E178">
@@ -4112,7 +4112,7 @@
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A179" s="5">
+      <c r="A179" s="7">
         <v>45759</v>
       </c>
       <c r="E179">
@@ -4129,7 +4129,7 @@
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A180" s="5">
+      <c r="A180" s="7">
         <v>45773</v>
       </c>
       <c r="C180">
@@ -4149,7 +4149,7 @@
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A181" s="5">
+      <c r="A181" s="7">
         <v>45780</v>
       </c>
       <c r="E181">
@@ -4166,7 +4166,7 @@
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A182" s="5">
+      <c r="A182" s="7">
         <v>45780</v>
       </c>
       <c r="E182">
@@ -4183,7 +4183,7 @@
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A183" s="5">
+      <c r="A183" s="7">
         <v>45801</v>
       </c>
       <c r="E183">
@@ -4200,7 +4200,7 @@
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A184" s="5">
+      <c r="A184" s="7">
         <v>45801</v>
       </c>
       <c r="E184">
@@ -4217,7 +4217,7 @@
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A185" s="5">
+      <c r="A185" s="7">
         <v>45801</v>
       </c>
       <c r="E185">
@@ -4234,7 +4234,7 @@
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A186" s="5">
+      <c r="A186" s="7">
         <v>45808</v>
       </c>
       <c r="C186">
@@ -4257,7 +4257,7 @@
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A187" s="5">
+      <c r="A187" s="7">
         <v>45815</v>
       </c>
       <c r="B187">
@@ -4274,7 +4274,7 @@
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A188" s="5">
+      <c r="A188" s="7">
         <v>45836</v>
       </c>
       <c r="B188">
@@ -4294,7 +4294,7 @@
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A189" s="5">
+      <c r="A189" s="7">
         <v>45843</v>
       </c>
       <c r="E189">
@@ -4311,7 +4311,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A190" s="5">
+      <c r="A190" s="7">
         <v>45843</v>
       </c>
       <c r="E190">
@@ -4328,7 +4328,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A191" s="5">
+      <c r="A191" s="7">
         <v>45850</v>
       </c>
       <c r="E191">
@@ -4345,7 +4345,7 @@
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A192" s="5">
+      <c r="A192" s="7">
         <v>45850</v>
       </c>
       <c r="E192">
@@ -4362,7 +4362,7 @@
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A193" s="5">
+      <c r="A193" s="7">
         <v>45857</v>
       </c>
       <c r="E193">
@@ -4379,7 +4379,7 @@
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A194" s="5">
+      <c r="A194" s="7">
         <v>45886</v>
       </c>
       <c r="E194">
@@ -4396,7 +4396,7 @@
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A195" s="5">
+      <c r="A195" s="7">
         <v>45892</v>
       </c>
       <c r="B195">
@@ -4416,7 +4416,7 @@
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A196" s="5">
+      <c r="A196" s="7">
         <v>45892</v>
       </c>
       <c r="E196">
@@ -4433,7 +4433,7 @@
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A197" s="5">
+      <c r="A197" s="7">
         <v>45899</v>
       </c>
       <c r="B197">
@@ -4808,7 +4808,7 @@
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A218" s="5">
+      <c r="A218" s="7">
         <v>45969</v>
       </c>
       <c r="C218">
@@ -4972,7 +4972,7 @@
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A228" s="5">
+      <c r="A228" s="7">
         <v>46005</v>
       </c>
       <c r="E228">
@@ -4989,7 +4989,7 @@
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A229" s="5">
+      <c r="A229" s="7">
         <v>46005</v>
       </c>
       <c r="E229">
@@ -5006,7 +5006,7 @@
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A230" s="5">
+      <c r="A230" s="7">
         <v>46012</v>
       </c>
       <c r="C230">
@@ -5026,7 +5026,7 @@
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A231" s="5">
+      <c r="A231" s="7">
         <v>46012</v>
       </c>
       <c r="E231">
@@ -5043,7 +5043,7 @@
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A232" s="5">
+      <c r="A232" s="7">
         <v>46012</v>
       </c>
       <c r="E232">
@@ -5060,7 +5060,7 @@
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A233" s="5">
+      <c r="A233" s="7">
         <v>46015</v>
       </c>
       <c r="B233">
@@ -5083,7 +5083,7 @@
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A234" s="5">
+      <c r="A234" s="7">
         <v>46016</v>
       </c>
       <c r="B234">
@@ -5106,7 +5106,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A235" s="5">
+      <c r="A235" s="7">
         <v>46020</v>
       </c>
       <c r="B235">
@@ -5129,7 +5129,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A236" s="5">
+      <c r="A236" s="7">
         <v>46032</v>
       </c>
       <c r="B236">
@@ -5143,7 +5143,7 @@
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A237" s="5">
+      <c r="A237" s="7">
         <v>46032</v>
       </c>
       <c r="B237">
@@ -5157,7 +5157,7 @@
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A238" s="5">
+      <c r="A238" s="7">
         <v>46039</v>
       </c>
       <c r="B238">
@@ -5174,7 +5174,7 @@
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A239" s="5">
+      <c r="A239" s="7">
         <v>46039</v>
       </c>
       <c r="B239">
@@ -5191,7 +5191,7 @@
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A240" s="5">
+      <c r="A240" s="7">
         <v>46039</v>
       </c>
       <c r="B240">
@@ -5208,7 +5208,7 @@
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A241" s="5">
+      <c r="A241" s="7">
         <v>46067</v>
       </c>
       <c r="B241">
@@ -5228,7 +5228,7 @@
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A242" s="5">
+      <c r="A242" s="7">
         <v>46067</v>
       </c>
       <c r="C242">
@@ -5245,7 +5245,7 @@
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A243" s="5">
+      <c r="A243" s="7">
         <v>46067</v>
       </c>
       <c r="B243">
@@ -5262,7 +5262,7 @@
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A244" s="5">
+      <c r="A244" s="7">
         <v>46067</v>
       </c>
       <c r="B244">
@@ -5279,7 +5279,7 @@
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A245" s="5">
+      <c r="A245" s="7">
         <v>46074</v>
       </c>
       <c r="B245">
@@ -5296,7 +5296,7 @@
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A246" s="5">
+      <c r="A246" s="7">
         <v>46074</v>
       </c>
       <c r="B246">
@@ -5313,7 +5313,7 @@
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A247" s="5">
+      <c r="A247" s="7">
         <v>46081</v>
       </c>
       <c r="B247">
@@ -5327,7 +5327,7 @@
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A248" s="5">
+      <c r="A248" s="7">
         <v>46081</v>
       </c>
       <c r="B248">
@@ -5341,7 +5341,7 @@
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A249" s="5">
+      <c r="A249" s="7">
         <v>46109</v>
       </c>
       <c r="B249">
@@ -5358,7 +5358,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A250" s="5">
+      <c r="A250" s="7">
         <v>46115</v>
       </c>
       <c r="B250">
@@ -5375,7 +5375,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A251" s="5">
+      <c r="A251" s="7">
         <v>46123</v>
       </c>
       <c r="B251">
@@ -5398,7 +5398,7 @@
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A252" s="5">
+      <c r="A252" s="7">
         <v>46130</v>
       </c>
       <c r="E252">
@@ -5415,7 +5415,7 @@
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A253" s="5">
+      <c r="A253" s="7">
         <v>46137</v>
       </c>
       <c r="E253">
@@ -5432,7 +5432,7 @@
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A254" s="5">
+      <c r="A254" s="7">
         <v>46144</v>
       </c>
       <c r="C254">
@@ -5452,7 +5452,7 @@
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A255" s="5">
+      <c r="A255" s="7">
         <v>46151</v>
       </c>
       <c r="C255">
@@ -5475,7 +5475,7 @@
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A256" s="5">
+      <c r="A256" s="7">
         <v>46151</v>
       </c>
       <c r="C256">
@@ -5498,7 +5498,7 @@
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A257" s="5">
+      <c r="A257" s="7">
         <v>46165</v>
       </c>
       <c r="E257">
@@ -5515,7 +5515,7 @@
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A258" s="5">
+      <c r="A258" s="7">
         <v>46165</v>
       </c>
       <c r="E258">
@@ -5532,7 +5532,7 @@
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A259" s="5">
+      <c r="A259" s="7">
         <v>46172</v>
       </c>
       <c r="B259">
@@ -5555,7 +5555,7 @@
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A260" s="5">
+      <c r="A260" s="7">
         <v>46172</v>
       </c>
       <c r="C260">
@@ -5575,7 +5575,7 @@
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A261" s="5">
+      <c r="A261" s="7">
         <v>46179</v>
       </c>
       <c r="C261">
@@ -5595,7 +5595,7 @@
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A262" s="5">
+      <c r="A262" s="7">
         <v>46186</v>
       </c>
       <c r="E262">
@@ -5612,7 +5612,7 @@
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A263" s="5">
+      <c r="A263" s="7">
         <v>46186</v>
       </c>
       <c r="E263">
@@ -5629,7 +5629,7 @@
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A264" s="5">
+      <c r="A264" s="7">
         <v>46186</v>
       </c>
       <c r="E264">
@@ -5646,7 +5646,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A265" s="5">
+      <c r="A265" s="7">
         <v>46193</v>
       </c>
       <c r="E265">
@@ -5663,7 +5663,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A266" s="5">
+      <c r="A266" s="7">
         <v>46194</v>
       </c>
       <c r="E266">
@@ -5680,7 +5680,7 @@
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A267" s="5">
+      <c r="A267" s="7">
         <v>46207</v>
       </c>
       <c r="E267">
@@ -5697,7 +5697,7 @@
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A268" s="5">
+      <c r="A268" s="7">
         <v>46207</v>
       </c>
       <c r="E268">

--- a/docs/Cottage Rummy Data File.xlsx
+++ b/docs/Cottage Rummy Data File.xlsx
@@ -2,35 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomku\Dropbox\Personal\Cottage Rummy Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0119320B-37D2-4C85-856F-D8D46CE937A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93E6D9C2-F228-49C8-936D-DA932CA2C25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="-15720" windowWidth="27915" windowHeight="14385" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="540" yWindow="-15720" windowWidth="27915" windowHeight="14385" xr2:uid="{E6534F6B-0E95-4988-B4BF-29B761CE070B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Input" sheetId="6" r:id="rId1"/>
+    <sheet name="Cottage Rummy Data File" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -40,6 +26,9 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>Date</t>
+  </si>
   <si>
     <t>Christine</t>
   </si>
@@ -61,22 +50,128 @@
   <si>
     <t>Tom</t>
   </si>
-  <si>
-    <t>Date</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd;@"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -84,20 +179,200 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -105,45 +380,208 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
-  </tableStyles>
-  <colors>
-    <mruColors>
-      <color rgb="FFF4BFBE"/>
-    </mruColors>
-  </colors>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -156,9 +594,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -166,39 +604,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -250,7 +688,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -302,7 +740,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -361,13 +799,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -376,6 +807,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -440,140 +878,123 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="3">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{5EAA29D7-D4FD-4ED6-9069-A41C45D10D62}">
-  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties>
-    <we:property name="claude.fileId" value="&quot;0819c0bc-6d73-4b54-bcd8-c2d5d2c69d40&quot;"/>
-  </we:properties>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AKI268"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B81E9E68-B537-4FF4-9CC7-FD38C9DF480D}">
+  <dimension ref="A1:H268"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>44580</v>
+      </c>
+      <c r="B2">
+        <v>225</v>
+      </c>
+      <c r="C2">
+        <v>390</v>
+      </c>
+      <c r="G2">
+        <v>290</v>
+      </c>
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="3"/>
-    </row>
-    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <v>44580</v>
       </c>
-      <c r="B2" s="4">
-        <v>225</v>
-      </c>
-      <c r="C2" s="4">
-        <v>390</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4">
-        <v>290</v>
-      </c>
-      <c r="H2" s="4">
-        <v>5</v>
-      </c>
-      <c r="J2"/>
-    </row>
-    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
+      <c r="C3">
+        <v>155</v>
+      </c>
+      <c r="D3">
+        <v>185</v>
+      </c>
+      <c r="G3">
+        <v>310</v>
+      </c>
+      <c r="H3">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
         <v>44580</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4">
-        <v>155</v>
-      </c>
-      <c r="D3" s="4">
-        <v>185</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4">
-        <v>310</v>
-      </c>
-      <c r="H3" s="4">
-        <v>295</v>
-      </c>
-      <c r="J3"/>
-    </row>
-    <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>44580</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4">
+      <c r="C4">
         <v>380</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4">
+      <c r="G4">
         <v>215</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4">
         <v>195</v>
       </c>
-      <c r="J4"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
         <v>44617</v>
       </c>
       <c r="B5">
@@ -592,8 +1013,8 @@
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>44618</v>
       </c>
       <c r="C6">
@@ -615,8 +1036,8 @@
         <v>520</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>44627</v>
       </c>
       <c r="C7">
@@ -632,8 +1053,8 @@
         <v>305</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
         <v>44632</v>
       </c>
       <c r="B8">
@@ -658,8 +1079,8 @@
         <v>375</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
         <v>44635</v>
       </c>
       <c r="B9">
@@ -684,8 +1105,8 @@
         <v>495</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
         <v>44636</v>
       </c>
       <c r="B10">
@@ -710,8 +1131,8 @@
         <v>425</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
         <v>44637</v>
       </c>
       <c r="B11">
@@ -736,8 +1157,8 @@
         <v>435</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
         <v>44666</v>
       </c>
       <c r="C12">
@@ -759,8 +1180,8 @@
         <v>460</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
         <v>44667</v>
       </c>
       <c r="B13">
@@ -785,8 +1206,8 @@
         <v>220</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="7">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
         <v>44681</v>
       </c>
       <c r="B14">
@@ -808,8 +1229,8 @@
         <v>410</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="7">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
         <v>44688</v>
       </c>
       <c r="C15">
@@ -828,8 +1249,8 @@
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="7">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
         <v>44695</v>
       </c>
       <c r="E16">
@@ -846,7 +1267,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="7">
+      <c r="A17" s="1">
         <v>44842</v>
       </c>
       <c r="B17">
@@ -866,7 +1287,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="7">
+      <c r="A18" s="1">
         <v>44849</v>
       </c>
       <c r="C18">
@@ -886,7 +1307,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="7">
+      <c r="A19" s="1">
         <v>44877</v>
       </c>
       <c r="C19">
@@ -906,7 +1327,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="7">
+      <c r="A20" s="1">
         <v>44884</v>
       </c>
       <c r="B20">
@@ -923,7 +1344,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="7">
+      <c r="A21" s="1">
         <v>44884</v>
       </c>
       <c r="B21">
@@ -940,7 +1361,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="7">
+      <c r="A22" s="1">
         <v>44905</v>
       </c>
       <c r="B22">
@@ -957,7 +1378,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="7">
+      <c r="A23" s="1">
         <v>44919</v>
       </c>
       <c r="B23">
@@ -983,7 +1404,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="7">
+      <c r="A24" s="1">
         <v>44920</v>
       </c>
       <c r="B24">
@@ -1009,7 +1430,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="7">
+      <c r="A25" s="1">
         <v>44921</v>
       </c>
       <c r="B25">
@@ -1035,7 +1456,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="7">
+      <c r="A26" s="1">
         <v>44923</v>
       </c>
       <c r="B26">
@@ -1055,7 +1476,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="7">
+      <c r="A27" s="1">
         <v>44924</v>
       </c>
       <c r="B27">
@@ -1081,7 +1502,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="7">
+      <c r="A28" s="1">
         <v>44925</v>
       </c>
       <c r="B28">
@@ -1107,7 +1528,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="7">
+      <c r="A29" s="1">
         <v>44926</v>
       </c>
       <c r="C29">
@@ -1130,7 +1551,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="7">
+      <c r="A30" s="1">
         <v>44926</v>
       </c>
       <c r="C30">
@@ -1153,7 +1574,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="7">
+      <c r="A31" s="1">
         <v>44927</v>
       </c>
       <c r="B31">
@@ -1179,7 +1600,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="7">
+      <c r="A32" s="1">
         <v>44927</v>
       </c>
       <c r="C32">
@@ -1196,7 +1617,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="7">
+      <c r="A33" s="1">
         <v>44947</v>
       </c>
       <c r="B33">
@@ -1219,7 +1640,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="7">
+      <c r="A34" s="1">
         <v>44947</v>
       </c>
       <c r="B34">
@@ -1239,7 +1660,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="7">
+      <c r="A35" s="1">
         <v>44952</v>
       </c>
       <c r="E35">
@@ -1256,7 +1677,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="7">
+      <c r="A36" s="1">
         <v>44952</v>
       </c>
       <c r="E36">
@@ -1273,7 +1694,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="7">
+      <c r="A37" s="1">
         <v>44953</v>
       </c>
       <c r="E37">
@@ -1290,7 +1711,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="7">
+      <c r="A38" s="1">
         <v>44953</v>
       </c>
       <c r="E38">
@@ -1307,7 +1728,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="7">
+      <c r="A39" s="1">
         <v>44957</v>
       </c>
       <c r="E39">
@@ -1324,7 +1745,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="7">
+      <c r="A40" s="1">
         <v>44958</v>
       </c>
       <c r="E40">
@@ -1341,7 +1762,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="7">
+      <c r="A41" s="1">
         <v>44959</v>
       </c>
       <c r="E41">
@@ -1358,7 +1779,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="7">
+      <c r="A42" s="1">
         <v>44959</v>
       </c>
       <c r="E42">
@@ -1375,7 +1796,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="7">
+      <c r="A43" s="1">
         <v>44960</v>
       </c>
       <c r="E43">
@@ -1392,7 +1813,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="7">
+      <c r="A44" s="1">
         <v>44961</v>
       </c>
       <c r="E44">
@@ -1409,7 +1830,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="7">
+      <c r="A45" s="1">
         <v>44961</v>
       </c>
       <c r="E45">
@@ -1426,7 +1847,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="7">
+      <c r="A46" s="1">
         <v>44962</v>
       </c>
       <c r="E46">
@@ -1443,7 +1864,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="7">
+      <c r="A47" s="1">
         <v>44996</v>
       </c>
       <c r="B47">
@@ -1469,7 +1890,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="7">
+      <c r="A48" s="1">
         <v>44982</v>
       </c>
       <c r="B48">
@@ -1486,7 +1907,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="7">
+      <c r="A49" s="1">
         <v>44982</v>
       </c>
       <c r="B49">
@@ -1503,7 +1924,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="7">
+      <c r="A50" s="1">
         <v>44982</v>
       </c>
       <c r="B50">
@@ -1520,7 +1941,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="7">
+      <c r="A51" s="1">
         <v>44989</v>
       </c>
       <c r="C51">
@@ -1534,7 +1955,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="7">
+      <c r="A52" s="1">
         <v>44989</v>
       </c>
       <c r="C52">
@@ -1548,7 +1969,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="7">
+      <c r="A53" s="1">
         <v>44989</v>
       </c>
       <c r="C53">
@@ -1562,7 +1983,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="7">
+      <c r="A54" s="1">
         <v>44996</v>
       </c>
       <c r="B54">
@@ -1588,7 +2009,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="7">
+      <c r="A55" s="1">
         <v>44996</v>
       </c>
       <c r="B55">
@@ -1614,7 +2035,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="7">
+      <c r="A56" s="1">
         <v>44998</v>
       </c>
       <c r="B56">
@@ -1640,7 +2061,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="7">
+      <c r="A57" s="1">
         <v>44999</v>
       </c>
       <c r="B57">
@@ -1663,7 +2084,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="7">
+      <c r="A58" s="1">
         <v>45010</v>
       </c>
       <c r="B58">
@@ -1680,7 +2101,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="7">
+      <c r="A59" s="1">
         <v>45017</v>
       </c>
       <c r="B59">
@@ -1697,7 +2118,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="7">
+      <c r="A60" s="1">
         <v>45017</v>
       </c>
       <c r="B60">
@@ -1714,7 +2135,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="7">
+      <c r="A61" s="1">
         <v>45038</v>
       </c>
       <c r="E61">
@@ -1731,7 +2152,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="7">
+      <c r="A62" s="1">
         <v>45045</v>
       </c>
       <c r="B62">
@@ -1754,7 +2175,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="7">
+      <c r="A63" s="1">
         <v>45052</v>
       </c>
       <c r="C63">
@@ -1774,7 +2195,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="7">
+      <c r="A64" s="1">
         <v>45066</v>
       </c>
       <c r="B64">
@@ -1800,7 +2221,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="7">
+      <c r="A65" s="1">
         <v>45067</v>
       </c>
       <c r="B65">
@@ -1820,7 +2241,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="7">
+      <c r="A66" s="1">
         <v>45068</v>
       </c>
       <c r="B66">
@@ -1840,7 +2261,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="7">
+      <c r="A67" s="1">
         <v>45094</v>
       </c>
       <c r="C67">
@@ -1863,7 +2284,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="7">
+      <c r="A68" s="1">
         <v>45101</v>
       </c>
       <c r="C68">
@@ -1883,7 +2304,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="7">
+      <c r="A69" s="1">
         <v>45101</v>
       </c>
       <c r="C69">
@@ -1903,7 +2324,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="7">
+      <c r="A70" s="1">
         <v>45115</v>
       </c>
       <c r="E70">
@@ -1920,7 +2341,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="7">
+      <c r="A71" s="1">
         <v>45115</v>
       </c>
       <c r="E71">
@@ -1937,7 +2358,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="7">
+      <c r="A72" s="1">
         <v>45122</v>
       </c>
       <c r="B72">
@@ -1957,7 +2378,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="7">
+      <c r="A73" s="1">
         <v>45129</v>
       </c>
       <c r="C73">
@@ -1980,7 +2401,7 @@
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="7">
+      <c r="A74" s="1">
         <v>45129</v>
       </c>
       <c r="C74">
@@ -2003,7 +2424,7 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="7">
+      <c r="A75" s="1">
         <v>45136</v>
       </c>
       <c r="E75">
@@ -2020,7 +2441,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="7">
+      <c r="A76" s="1">
         <v>45144</v>
       </c>
       <c r="D76">
@@ -2040,7 +2461,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="7">
+      <c r="A77" s="1">
         <v>45150</v>
       </c>
       <c r="C77">
@@ -2063,7 +2484,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="7">
+      <c r="A78" s="1">
         <v>45151</v>
       </c>
       <c r="C78">
@@ -2086,7 +2507,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="7">
+      <c r="A79" s="1">
         <v>45157</v>
       </c>
       <c r="B79">
@@ -2106,7 +2527,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="7">
+      <c r="A80" s="1">
         <v>45178</v>
       </c>
       <c r="B80">
@@ -2126,7 +2547,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="7">
+      <c r="A81" s="1">
         <v>45179</v>
       </c>
       <c r="C81">
@@ -2146,7 +2567,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="7">
+      <c r="A82" s="1">
         <v>45213</v>
       </c>
       <c r="B82">
@@ -2169,7 +2590,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="7">
+      <c r="A83" s="1">
         <v>45213</v>
       </c>
       <c r="C83">
@@ -2189,7 +2610,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="7">
+      <c r="A84" s="1">
         <v>45227</v>
       </c>
       <c r="C84">
@@ -2209,7 +2630,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="7">
+      <c r="A85" s="1">
         <v>45248</v>
       </c>
       <c r="B85">
@@ -2226,7 +2647,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="7">
+      <c r="A86" s="1">
         <v>45255</v>
       </c>
       <c r="B86">
@@ -2243,7 +2664,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="7">
+      <c r="A87" s="1">
         <v>45255</v>
       </c>
       <c r="B87">
@@ -2260,7 +2681,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="7">
+      <c r="A88" s="1">
         <v>45263</v>
       </c>
       <c r="B88">
@@ -2277,7 +2698,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="7">
+      <c r="A89" s="1">
         <v>45263</v>
       </c>
       <c r="B89">
@@ -2294,7 +2715,7 @@
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="7">
+      <c r="A90" s="1">
         <v>45269</v>
       </c>
       <c r="B90">
@@ -2311,7 +2732,7 @@
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="7">
+      <c r="A91" s="1">
         <v>45269</v>
       </c>
       <c r="B91">
@@ -2328,7 +2749,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="7">
+      <c r="A92" s="1">
         <v>45269</v>
       </c>
       <c r="B92">
@@ -2345,7 +2766,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="7">
+      <c r="A93" s="1">
         <v>45283</v>
       </c>
       <c r="E93">
@@ -2362,7 +2783,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="7">
+      <c r="A94" s="1">
         <v>45283</v>
       </c>
       <c r="E94">
@@ -2379,7 +2800,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="7">
+      <c r="A95" s="1">
         <v>45283</v>
       </c>
       <c r="E95">
@@ -2396,7 +2817,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="7">
+      <c r="A96" s="1">
         <v>45284</v>
       </c>
       <c r="B96">
@@ -2422,7 +2843,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="7">
+      <c r="A97" s="1">
         <v>45285</v>
       </c>
       <c r="B97">
@@ -2448,7 +2869,7 @@
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="7">
+      <c r="A98" s="1">
         <v>45285</v>
       </c>
       <c r="B98">
@@ -2474,7 +2895,7 @@
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="7">
+      <c r="A99" s="1">
         <v>45286</v>
       </c>
       <c r="C99">
@@ -2494,7 +2915,7 @@
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="7">
+      <c r="A100" s="1">
         <v>45286</v>
       </c>
       <c r="B100">
@@ -2520,7 +2941,7 @@
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="7">
+      <c r="A101" s="1">
         <v>45290</v>
       </c>
       <c r="B101">
@@ -2546,7 +2967,7 @@
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="7">
+      <c r="A102" s="1">
         <v>45291</v>
       </c>
       <c r="C102">
@@ -2566,7 +2987,7 @@
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="7">
+      <c r="A103" s="1">
         <v>45297</v>
       </c>
       <c r="B103">
@@ -2589,7 +3010,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="7">
+      <c r="A104" s="1">
         <v>45297</v>
       </c>
       <c r="B104">
@@ -2612,7 +3033,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="7">
+      <c r="A105" s="1">
         <v>45304</v>
       </c>
       <c r="B105">
@@ -2632,7 +3053,7 @@
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="7">
+      <c r="A106" s="1">
         <v>45304</v>
       </c>
       <c r="B106">
@@ -2655,7 +3076,7 @@
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="7">
+      <c r="A107" s="1">
         <v>45318</v>
       </c>
       <c r="B107">
@@ -2672,7 +3093,7 @@
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="7">
+      <c r="A108" s="1">
         <v>45318</v>
       </c>
       <c r="B108">
@@ -2689,7 +3110,7 @@
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="7">
+      <c r="A109" s="1">
         <v>45325</v>
       </c>
       <c r="B109">
@@ -2706,7 +3127,7 @@
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="7">
+      <c r="A110" s="1">
         <v>45325</v>
       </c>
       <c r="B110">
@@ -2723,7 +3144,7 @@
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="7">
+      <c r="A111" s="1">
         <v>45346</v>
       </c>
       <c r="B111">
@@ -2740,7 +3161,7 @@
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="7">
+      <c r="A112" s="1">
         <v>45346</v>
       </c>
       <c r="B112">
@@ -2757,7 +3178,7 @@
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="7">
+      <c r="A113" s="1">
         <v>45356</v>
       </c>
       <c r="C113">
@@ -2780,7 +3201,7 @@
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="7">
+      <c r="A114" s="1">
         <v>45357</v>
       </c>
       <c r="C114">
@@ -2800,7 +3221,7 @@
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="7">
+      <c r="A115" s="1">
         <v>45358</v>
       </c>
       <c r="C115">
@@ -2820,7 +3241,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="7">
+      <c r="A116" s="1">
         <v>45358</v>
       </c>
       <c r="C116">
@@ -2840,7 +3261,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="7">
+      <c r="A117" s="1">
         <v>45374</v>
       </c>
       <c r="B117">
@@ -2857,7 +3278,7 @@
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="7">
+      <c r="A118" s="1">
         <v>45374</v>
       </c>
       <c r="B118">
@@ -2874,7 +3295,7 @@
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="7">
+      <c r="A119" s="1">
         <v>45388</v>
       </c>
       <c r="B119">
@@ -2891,7 +3312,7 @@
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="7">
+      <c r="A120" s="1">
         <v>45402</v>
       </c>
       <c r="C120">
@@ -2911,7 +3332,7 @@
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="7">
+      <c r="A121" s="1">
         <v>45409</v>
       </c>
       <c r="B121">
@@ -2928,7 +3349,7 @@
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A122" s="7">
+      <c r="A122" s="1">
         <v>45416</v>
       </c>
       <c r="C122">
@@ -2948,7 +3369,7 @@
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" s="7">
+      <c r="A123" s="1">
         <v>45416</v>
       </c>
       <c r="C123">
@@ -2968,7 +3389,7 @@
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="7">
+      <c r="A124" s="1">
         <v>45423</v>
       </c>
       <c r="E124">
@@ -2985,7 +3406,7 @@
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="7">
+      <c r="A125" s="1">
         <v>45423</v>
       </c>
       <c r="E125">
@@ -3002,7 +3423,7 @@
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="7">
+      <c r="A126" s="1">
         <v>45437</v>
       </c>
       <c r="C126">
@@ -3022,7 +3443,7 @@
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" s="7">
+      <c r="A127" s="1">
         <v>45437</v>
       </c>
       <c r="C127">
@@ -3042,7 +3463,7 @@
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" s="7">
+      <c r="A128" s="1">
         <v>45444</v>
       </c>
       <c r="C128">
@@ -3061,8 +3482,8 @@
         <v>240</v>
       </c>
     </row>
-    <row r="129" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A129" s="7">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
         <v>45451</v>
       </c>
       <c r="E129">
@@ -3078,8 +3499,8 @@
         <v>305</v>
       </c>
     </row>
-    <row r="130" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A130" s="7">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
         <v>45465</v>
       </c>
       <c r="E130">
@@ -3095,8 +3516,8 @@
         <v>365</v>
       </c>
     </row>
-    <row r="131" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A131" s="7">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
         <v>45501</v>
       </c>
       <c r="C131">
@@ -3115,8 +3536,8 @@
         <v>575</v>
       </c>
     </row>
-    <row r="132" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A132" s="7">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
         <v>45507</v>
       </c>
       <c r="C132">
@@ -3135,8 +3556,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="133" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A133" s="7">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
         <v>45559</v>
       </c>
       <c r="C133">
@@ -3154,131 +3575,9 @@
       <c r="H133">
         <v>585</v>
       </c>
-      <c r="I133" s="1"/>
-      <c r="K133" s="1"/>
-      <c r="S133" s="1"/>
-      <c r="AA133" s="1"/>
-      <c r="AI133" s="1"/>
-      <c r="AQ133" s="1"/>
-      <c r="AY133" s="1"/>
-      <c r="BG133" s="1"/>
-      <c r="BO133" s="1"/>
-      <c r="BW133" s="1"/>
-      <c r="CE133" s="1"/>
-      <c r="CM133" s="1"/>
-      <c r="CU133" s="1"/>
-      <c r="DC133" s="1"/>
-      <c r="DK133" s="1"/>
-      <c r="DS133" s="1"/>
-      <c r="EA133" s="1"/>
-      <c r="EI133" s="1"/>
-      <c r="EQ133" s="1"/>
-      <c r="EY133" s="1"/>
-      <c r="FG133" s="1"/>
-      <c r="FO133" s="1"/>
-      <c r="FW133" s="1"/>
-      <c r="GE133" s="1"/>
-      <c r="GM133" s="1"/>
-      <c r="GU133" s="1"/>
-      <c r="HC133" s="1"/>
-      <c r="HK133" s="1"/>
-      <c r="HS133" s="1"/>
-      <c r="IA133" s="1"/>
-      <c r="II133" s="1"/>
-      <c r="IQ133" s="1"/>
-      <c r="IY133" s="1"/>
-      <c r="JG133" s="1"/>
-      <c r="JO133" s="1"/>
-      <c r="JW133" s="1"/>
-      <c r="KE133" s="1"/>
-      <c r="KM133" s="1"/>
-      <c r="KU133" s="1"/>
-      <c r="LC133" s="1"/>
-      <c r="LK133" s="1"/>
-      <c r="LS133" s="1"/>
-      <c r="MA133" s="1"/>
-      <c r="MI133" s="1"/>
-      <c r="MQ133" s="1"/>
-      <c r="MY133" s="1"/>
-      <c r="NG133" s="1"/>
-      <c r="NO133" s="1"/>
-      <c r="NW133" s="1"/>
-      <c r="OE133" s="1"/>
-      <c r="OM133" s="1"/>
-      <c r="OU133" s="1"/>
-      <c r="PC133" s="1"/>
-      <c r="PK133" s="1"/>
-      <c r="PS133" s="1"/>
-      <c r="QA133" s="1"/>
-      <c r="QI133" s="1"/>
-      <c r="QQ133" s="1"/>
-      <c r="QY133" s="1"/>
-      <c r="RG133" s="1"/>
-      <c r="RO133" s="1"/>
-      <c r="RW133" s="1"/>
-      <c r="SE133" s="1"/>
-      <c r="SM133" s="1"/>
-      <c r="SU133" s="1"/>
-      <c r="TC133" s="1"/>
-      <c r="TK133" s="1"/>
-      <c r="TS133" s="1"/>
-      <c r="UA133" s="1"/>
-      <c r="UI133" s="1"/>
-      <c r="UQ133" s="1"/>
-      <c r="UY133" s="1"/>
-      <c r="VG133" s="1"/>
-      <c r="VO133" s="1"/>
-      <c r="VW133" s="1"/>
-      <c r="WE133" s="1"/>
-      <c r="WM133" s="1"/>
-      <c r="WU133" s="1"/>
-      <c r="XC133" s="1"/>
-      <c r="XK133" s="1"/>
-      <c r="XS133" s="1"/>
-      <c r="YA133" s="1"/>
-      <c r="YI133" s="1"/>
-      <c r="YQ133" s="1"/>
-      <c r="YY133" s="1"/>
-      <c r="ZG133" s="1"/>
-      <c r="ZO133" s="1"/>
-      <c r="ZW133" s="1"/>
-      <c r="AAE133" s="1"/>
-      <c r="AAM133" s="1"/>
-      <c r="AAU133" s="1"/>
-      <c r="ABC133" s="1"/>
-      <c r="ABK133" s="1"/>
-      <c r="ABS133" s="1"/>
-      <c r="ACA133" s="1"/>
-      <c r="ACI133" s="1"/>
-      <c r="ACQ133" s="1"/>
-      <c r="ACY133" s="1"/>
-      <c r="ADG133" s="1"/>
-      <c r="ADO133" s="1"/>
-      <c r="ADW133" s="1"/>
-      <c r="AEE133" s="1"/>
-      <c r="AEM133" s="1"/>
-      <c r="AEU133" s="1"/>
-      <c r="AFC133" s="1"/>
-      <c r="AFK133" s="1"/>
-      <c r="AFS133" s="1"/>
-      <c r="AGA133" s="1"/>
-      <c r="AGI133" s="1"/>
-      <c r="AGQ133" s="1"/>
-      <c r="AGY133" s="1"/>
-      <c r="AHG133" s="1"/>
-      <c r="AHO133" s="1"/>
-      <c r="AHW133" s="1"/>
-      <c r="AIE133" s="1"/>
-      <c r="AIM133" s="1"/>
-      <c r="AIU133" s="1"/>
-      <c r="AJC133" s="1"/>
-      <c r="AJK133" s="1"/>
-      <c r="AJS133" s="1"/>
-      <c r="AKA133" s="1"/>
-      <c r="AKI133" s="1"/>
-    </row>
-    <row r="134" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A134" s="7">
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
         <v>45514</v>
       </c>
       <c r="E134">
@@ -3294,8 +3593,8 @@
         <v>455</v>
       </c>
     </row>
-    <row r="135" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A135" s="7">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
         <v>45521</v>
       </c>
       <c r="B135">
@@ -3311,8 +3610,8 @@
         <v>240</v>
       </c>
     </row>
-    <row r="136" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A136" s="7">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
         <v>45559</v>
       </c>
       <c r="C136">
@@ -3331,8 +3630,8 @@
         <v>585</v>
       </c>
     </row>
-    <row r="137" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A137" s="7">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
         <v>45535</v>
       </c>
       <c r="B137">
@@ -3348,8 +3647,8 @@
         <v>400</v>
       </c>
     </row>
-    <row r="138" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A138" s="7">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
         <v>45542</v>
       </c>
       <c r="E138">
@@ -3365,8 +3664,8 @@
         <v>160</v>
       </c>
     </row>
-    <row r="139" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A139" s="7">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
         <v>45550</v>
       </c>
       <c r="E139">
@@ -3382,8 +3681,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A140" s="7">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
         <v>45556</v>
       </c>
       <c r="B140">
@@ -3399,8 +3698,8 @@
         <v>190</v>
       </c>
     </row>
-    <row r="141" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A141" s="7">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
         <v>45563</v>
       </c>
       <c r="C141">
@@ -3419,8 +3718,8 @@
         <v>365</v>
       </c>
     </row>
-    <row r="142" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A142" s="7">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
         <v>45570</v>
       </c>
       <c r="E142">
@@ -3436,8 +3735,8 @@
         <v>315</v>
       </c>
     </row>
-    <row r="143" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A143" s="7">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
         <v>45570</v>
       </c>
       <c r="E143">
@@ -3453,8 +3752,8 @@
         <v>310</v>
       </c>
     </row>
-    <row r="144" spans="1:971" x14ac:dyDescent="0.3">
-      <c r="A144" s="7">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
         <v>45570</v>
       </c>
       <c r="E144">
@@ -3471,7 +3770,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A145" s="7">
+      <c r="A145" s="1">
         <v>45577</v>
       </c>
       <c r="E145">
@@ -3488,7 +3787,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A146" s="7">
+      <c r="A146" s="1">
         <v>45591</v>
       </c>
       <c r="E146">
@@ -3505,7 +3804,7 @@
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A147" s="7">
+      <c r="A147" s="1">
         <v>45619</v>
       </c>
       <c r="B147">
@@ -3522,7 +3821,7 @@
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A148" s="7">
+      <c r="A148" s="1">
         <v>45631</v>
       </c>
       <c r="B148">
@@ -3539,7 +3838,7 @@
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A149" s="7">
+      <c r="A149" s="1">
         <v>45647</v>
       </c>
       <c r="C149">
@@ -3559,7 +3858,7 @@
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A150" s="7">
+      <c r="A150" s="1">
         <v>45647</v>
       </c>
       <c r="E150">
@@ -3576,7 +3875,7 @@
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A151" s="7">
+      <c r="A151" s="1">
         <v>45650</v>
       </c>
       <c r="B151">
@@ -3599,7 +3898,7 @@
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A152" s="7">
+      <c r="A152" s="1">
         <v>45650</v>
       </c>
       <c r="C152">
@@ -3619,7 +3918,7 @@
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A153" s="7">
+      <c r="A153" s="1">
         <v>45651</v>
       </c>
       <c r="B153">
@@ -3642,7 +3941,7 @@
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A154" s="7">
+      <c r="A154" s="1">
         <v>45651</v>
       </c>
       <c r="C154">
@@ -3662,7 +3961,7 @@
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A155" s="7">
+      <c r="A155" s="1">
         <v>45652</v>
       </c>
       <c r="B155">
@@ -3685,7 +3984,7 @@
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A156" s="7">
+      <c r="A156" s="1">
         <v>45652</v>
       </c>
       <c r="C156">
@@ -3705,7 +4004,7 @@
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A157" s="7">
+      <c r="A157" s="1">
         <v>45654</v>
       </c>
       <c r="B157">
@@ -3731,7 +4030,7 @@
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A158" s="7">
+      <c r="A158" s="1">
         <v>45654</v>
       </c>
       <c r="C158">
@@ -3754,7 +4053,7 @@
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A159" s="7">
+      <c r="A159" s="1">
         <v>45655</v>
       </c>
       <c r="B159">
@@ -3774,7 +4073,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A160" s="7">
+      <c r="A160" s="1">
         <v>45657</v>
       </c>
       <c r="C160">
@@ -3797,7 +4096,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A161" s="7">
+      <c r="A161" s="1">
         <v>45657</v>
       </c>
       <c r="C161">
@@ -3820,7 +4119,7 @@
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A162" s="7">
+      <c r="A162" s="1">
         <v>45658</v>
       </c>
       <c r="B162">
@@ -3846,7 +4145,7 @@
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A163" s="7">
+      <c r="A163" s="1">
         <v>45661</v>
       </c>
       <c r="B163">
@@ -3872,7 +4171,7 @@
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A164" s="7">
+      <c r="A164" s="1">
         <v>45668</v>
       </c>
       <c r="B164">
@@ -3886,7 +4185,7 @@
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A165" s="7">
+      <c r="A165" s="1">
         <v>45675</v>
       </c>
       <c r="B165">
@@ -3903,7 +4202,7 @@
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A166" s="7">
+      <c r="A166" s="1">
         <v>45675</v>
       </c>
       <c r="C166">
@@ -3917,7 +4216,7 @@
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A167" s="7">
+      <c r="A167" s="1">
         <v>45682</v>
       </c>
       <c r="B167">
@@ -3934,7 +4233,7 @@
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A168" s="7">
+      <c r="A168" s="1">
         <v>45682</v>
       </c>
       <c r="C168">
@@ -3948,7 +4247,7 @@
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A169" s="7">
+      <c r="A169" s="1">
         <v>45689</v>
       </c>
       <c r="B169">
@@ -3968,7 +4267,7 @@
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A170" s="7">
+      <c r="A170" s="1">
         <v>45696</v>
       </c>
       <c r="C170">
@@ -3982,7 +4281,7 @@
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A171" s="7">
+      <c r="A171" s="1">
         <v>45696</v>
       </c>
       <c r="C171">
@@ -3996,7 +4295,7 @@
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A172" s="7">
+      <c r="A172" s="1">
         <v>45696</v>
       </c>
       <c r="C172">
@@ -4010,7 +4309,7 @@
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A173" s="7">
+      <c r="A173" s="1">
         <v>45705</v>
       </c>
       <c r="C173">
@@ -4024,7 +4323,7 @@
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A174" s="7">
+      <c r="A174" s="1">
         <v>45737</v>
       </c>
       <c r="E174">
@@ -4041,7 +4340,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A175" s="7">
+      <c r="A175" s="1">
         <v>45740</v>
       </c>
       <c r="E175">
@@ -4058,7 +4357,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A176" s="7">
+      <c r="A176" s="1">
         <v>45746</v>
       </c>
       <c r="E176">
@@ -4075,7 +4374,7 @@
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A177" s="7">
+      <c r="A177" s="1">
         <v>45752</v>
       </c>
       <c r="B177">
@@ -4095,7 +4394,7 @@
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A178" s="7">
+      <c r="A178" s="1">
         <v>45752</v>
       </c>
       <c r="E178">
@@ -4112,7 +4411,7 @@
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A179" s="7">
+      <c r="A179" s="1">
         <v>45759</v>
       </c>
       <c r="E179">
@@ -4129,7 +4428,7 @@
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A180" s="7">
+      <c r="A180" s="1">
         <v>45773</v>
       </c>
       <c r="C180">
@@ -4149,7 +4448,7 @@
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A181" s="7">
+      <c r="A181" s="1">
         <v>45780</v>
       </c>
       <c r="E181">
@@ -4166,7 +4465,7 @@
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A182" s="7">
+      <c r="A182" s="1">
         <v>45780</v>
       </c>
       <c r="E182">
@@ -4183,7 +4482,7 @@
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A183" s="7">
+      <c r="A183" s="1">
         <v>45801</v>
       </c>
       <c r="E183">
@@ -4200,7 +4499,7 @@
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A184" s="7">
+      <c r="A184" s="1">
         <v>45801</v>
       </c>
       <c r="E184">
@@ -4217,7 +4516,7 @@
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A185" s="7">
+      <c r="A185" s="1">
         <v>45801</v>
       </c>
       <c r="E185">
@@ -4234,7 +4533,7 @@
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A186" s="7">
+      <c r="A186" s="1">
         <v>45808</v>
       </c>
       <c r="C186">
@@ -4257,7 +4556,7 @@
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A187" s="7">
+      <c r="A187" s="1">
         <v>45815</v>
       </c>
       <c r="B187">
@@ -4274,7 +4573,7 @@
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A188" s="7">
+      <c r="A188" s="1">
         <v>45836</v>
       </c>
       <c r="B188">
@@ -4294,7 +4593,7 @@
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A189" s="7">
+      <c r="A189" s="1">
         <v>45843</v>
       </c>
       <c r="E189">
@@ -4311,7 +4610,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A190" s="7">
+      <c r="A190" s="1">
         <v>45843</v>
       </c>
       <c r="E190">
@@ -4328,7 +4627,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A191" s="7">
+      <c r="A191" s="1">
         <v>45850</v>
       </c>
       <c r="E191">
@@ -4345,7 +4644,7 @@
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A192" s="7">
+      <c r="A192" s="1">
         <v>45850</v>
       </c>
       <c r="E192">
@@ -4362,7 +4661,7 @@
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A193" s="7">
+      <c r="A193" s="1">
         <v>45857</v>
       </c>
       <c r="E193">
@@ -4379,7 +4678,7 @@
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A194" s="7">
+      <c r="A194" s="1">
         <v>45886</v>
       </c>
       <c r="E194">
@@ -4396,7 +4695,7 @@
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A195" s="7">
+      <c r="A195" s="1">
         <v>45892</v>
       </c>
       <c r="B195">
@@ -4416,7 +4715,7 @@
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A196" s="7">
+      <c r="A196" s="1">
         <v>45892</v>
       </c>
       <c r="E196">
@@ -4433,7 +4732,7 @@
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A197" s="7">
+      <c r="A197" s="1">
         <v>45899</v>
       </c>
       <c r="B197">
@@ -4450,7 +4749,7 @@
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A198" s="8">
+      <c r="A198" s="1">
         <v>45906</v>
       </c>
       <c r="B198">
@@ -4473,7 +4772,7 @@
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A199" s="8">
+      <c r="A199" s="1">
         <v>45906</v>
       </c>
       <c r="C199">
@@ -4493,7 +4792,7 @@
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A200" s="8">
+      <c r="A200" s="1">
         <v>45913</v>
       </c>
       <c r="B200">
@@ -4507,7 +4806,7 @@
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A201" s="8">
+      <c r="A201" s="1">
         <v>45913</v>
       </c>
       <c r="C201">
@@ -4527,7 +4826,7 @@
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A202" s="8">
+      <c r="A202" s="1">
         <v>45920</v>
       </c>
       <c r="E202">
@@ -4544,7 +4843,7 @@
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A203" s="8">
+      <c r="A203" s="1">
         <v>45928</v>
       </c>
       <c r="E203">
@@ -4561,7 +4860,7 @@
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A204" s="8">
+      <c r="A204" s="1">
         <v>45930</v>
       </c>
       <c r="E204">
@@ -4578,7 +4877,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A205" s="8">
+      <c r="A205" s="1">
         <v>45932</v>
       </c>
       <c r="E205">
@@ -4595,7 +4894,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A206" s="8">
+      <c r="A206" s="1">
         <v>45933</v>
       </c>
       <c r="E206">
@@ -4612,7 +4911,7 @@
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A207" s="8">
+      <c r="A207" s="1">
         <v>45934</v>
       </c>
       <c r="E207">
@@ -4629,7 +4928,7 @@
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A208" s="8">
+      <c r="A208" s="1">
         <v>45935</v>
       </c>
       <c r="E208">
@@ -4646,7 +4945,7 @@
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A209" s="8">
+      <c r="A209" s="1">
         <v>45935</v>
       </c>
       <c r="E209">
@@ -4663,7 +4962,7 @@
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A210" s="8">
+      <c r="A210" s="1">
         <v>45936</v>
       </c>
       <c r="E210">
@@ -4680,7 +4979,7 @@
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A211" s="8">
+      <c r="A211" s="1">
         <v>45940</v>
       </c>
       <c r="C211">
@@ -4703,7 +5002,7 @@
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A212" s="8">
+      <c r="A212" s="1">
         <v>45942</v>
       </c>
       <c r="C212">
@@ -4720,7 +5019,7 @@
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A213" s="8">
+      <c r="A213" s="1">
         <v>45942</v>
       </c>
       <c r="C213">
@@ -4737,7 +5036,7 @@
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A214" s="8">
+      <c r="A214" s="1">
         <v>45948</v>
       </c>
       <c r="E214">
@@ -4754,7 +5053,7 @@
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A215" s="8">
+      <c r="A215" s="1">
         <v>45948</v>
       </c>
       <c r="E215">
@@ -4771,7 +5070,7 @@
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A216" s="8">
+      <c r="A216" s="1">
         <v>45955</v>
       </c>
       <c r="C216">
@@ -4788,7 +5087,7 @@
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A217" s="8">
+      <c r="A217" s="1">
         <v>45962</v>
       </c>
       <c r="C217">
@@ -4808,7 +5107,7 @@
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A218" s="7">
+      <c r="A218" s="1">
         <v>45969</v>
       </c>
       <c r="C218">
@@ -4831,7 +5130,7 @@
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A219" s="8">
+      <c r="A219" s="1">
         <v>45983</v>
       </c>
       <c r="B219">
@@ -4848,7 +5147,7 @@
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A220" s="8">
+      <c r="A220" s="1">
         <v>45983</v>
       </c>
       <c r="B220">
@@ -4865,7 +5164,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A221" s="8">
+      <c r="A221" s="1">
         <v>45990</v>
       </c>
       <c r="C221">
@@ -4879,7 +5178,7 @@
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A222" s="8">
+      <c r="A222" s="1">
         <v>45990</v>
       </c>
       <c r="C222">
@@ -4893,7 +5192,7 @@
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A223" s="8">
+      <c r="A223" s="1">
         <v>45990</v>
       </c>
       <c r="C223">
@@ -4907,7 +5206,7 @@
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A224" s="8">
+      <c r="A224" s="1">
         <v>45990</v>
       </c>
       <c r="C224">
@@ -4921,7 +5220,7 @@
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A225" s="8">
+      <c r="A225" s="1">
         <v>45997</v>
       </c>
       <c r="B225">
@@ -4938,7 +5237,7 @@
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A226" s="8">
+      <c r="A226" s="1">
         <v>45997</v>
       </c>
       <c r="B226">
@@ -4955,7 +5254,7 @@
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A227" s="8">
+      <c r="A227" s="1">
         <v>45997</v>
       </c>
       <c r="B227">
@@ -4972,7 +5271,7 @@
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A228" s="7">
+      <c r="A228" s="1">
         <v>46005</v>
       </c>
       <c r="E228">
@@ -4989,7 +5288,7 @@
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A229" s="7">
+      <c r="A229" s="1">
         <v>46005</v>
       </c>
       <c r="E229">
@@ -5006,7 +5305,7 @@
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A230" s="7">
+      <c r="A230" s="1">
         <v>46012</v>
       </c>
       <c r="C230">
@@ -5026,7 +5325,7 @@
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A231" s="7">
+      <c r="A231" s="1">
         <v>46012</v>
       </c>
       <c r="E231">
@@ -5043,7 +5342,7 @@
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A232" s="7">
+      <c r="A232" s="1">
         <v>46012</v>
       </c>
       <c r="E232">
@@ -5060,7 +5359,7 @@
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A233" s="7">
+      <c r="A233" s="1">
         <v>46015</v>
       </c>
       <c r="B233">
@@ -5083,7 +5382,7 @@
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A234" s="7">
+      <c r="A234" s="1">
         <v>46016</v>
       </c>
       <c r="B234">
@@ -5106,7 +5405,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A235" s="7">
+      <c r="A235" s="1">
         <v>46020</v>
       </c>
       <c r="B235">
@@ -5129,7 +5428,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A236" s="7">
+      <c r="A236" s="1">
         <v>46032</v>
       </c>
       <c r="B236">
@@ -5143,7 +5442,7 @@
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A237" s="7">
+      <c r="A237" s="1">
         <v>46032</v>
       </c>
       <c r="B237">
@@ -5157,7 +5456,7 @@
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A238" s="7">
+      <c r="A238" s="1">
         <v>46039</v>
       </c>
       <c r="B238">
@@ -5174,7 +5473,7 @@
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A239" s="7">
+      <c r="A239" s="1">
         <v>46039</v>
       </c>
       <c r="B239">
@@ -5191,7 +5490,7 @@
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A240" s="7">
+      <c r="A240" s="1">
         <v>46039</v>
       </c>
       <c r="B240">
@@ -5208,7 +5507,7 @@
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A241" s="7">
+      <c r="A241" s="1">
         <v>46067</v>
       </c>
       <c r="B241">
@@ -5228,7 +5527,7 @@
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A242" s="7">
+      <c r="A242" s="1">
         <v>46067</v>
       </c>
       <c r="C242">
@@ -5245,7 +5544,7 @@
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A243" s="7">
+      <c r="A243" s="1">
         <v>46067</v>
       </c>
       <c r="B243">
@@ -5262,7 +5561,7 @@
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A244" s="7">
+      <c r="A244" s="1">
         <v>46067</v>
       </c>
       <c r="B244">
@@ -5279,7 +5578,7 @@
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A245" s="7">
+      <c r="A245" s="1">
         <v>46074</v>
       </c>
       <c r="B245">
@@ -5296,7 +5595,7 @@
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A246" s="7">
+      <c r="A246" s="1">
         <v>46074</v>
       </c>
       <c r="B246">
@@ -5313,7 +5612,7 @@
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A247" s="7">
+      <c r="A247" s="1">
         <v>46081</v>
       </c>
       <c r="B247">
@@ -5327,7 +5626,7 @@
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A248" s="7">
+      <c r="A248" s="1">
         <v>46081</v>
       </c>
       <c r="B248">
@@ -5341,7 +5640,7 @@
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A249" s="7">
+      <c r="A249" s="1">
         <v>46109</v>
       </c>
       <c r="B249">
@@ -5358,7 +5657,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A250" s="7">
+      <c r="A250" s="1">
         <v>46115</v>
       </c>
       <c r="B250">
@@ -5375,7 +5674,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A251" s="7">
+      <c r="A251" s="1">
         <v>46123</v>
       </c>
       <c r="B251">
@@ -5398,7 +5697,7 @@
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A252" s="7">
+      <c r="A252" s="1">
         <v>46130</v>
       </c>
       <c r="E252">
@@ -5415,7 +5714,7 @@
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A253" s="7">
+      <c r="A253" s="1">
         <v>46137</v>
       </c>
       <c r="E253">
@@ -5432,7 +5731,7 @@
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A254" s="7">
+      <c r="A254" s="1">
         <v>46144</v>
       </c>
       <c r="C254">
@@ -5452,7 +5751,7 @@
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A255" s="7">
+      <c r="A255" s="1">
         <v>46151</v>
       </c>
       <c r="C255">
@@ -5475,7 +5774,7 @@
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A256" s="7">
+      <c r="A256" s="1">
         <v>46151</v>
       </c>
       <c r="C256">
@@ -5498,7 +5797,7 @@
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A257" s="7">
+      <c r="A257" s="1">
         <v>46165</v>
       </c>
       <c r="E257">
@@ -5515,7 +5814,7 @@
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A258" s="7">
+      <c r="A258" s="1">
         <v>46165</v>
       </c>
       <c r="E258">
@@ -5532,7 +5831,7 @@
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A259" s="7">
+      <c r="A259" s="1">
         <v>46172</v>
       </c>
       <c r="B259">
@@ -5555,7 +5854,7 @@
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A260" s="7">
+      <c r="A260" s="1">
         <v>46172</v>
       </c>
       <c r="C260">
@@ -5575,7 +5874,7 @@
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A261" s="7">
+      <c r="A261" s="1">
         <v>46179</v>
       </c>
       <c r="C261">
@@ -5595,7 +5894,7 @@
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A262" s="7">
+      <c r="A262" s="1">
         <v>46186</v>
       </c>
       <c r="E262">
@@ -5612,7 +5911,7 @@
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A263" s="7">
+      <c r="A263" s="1">
         <v>46186</v>
       </c>
       <c r="E263">
@@ -5629,7 +5928,7 @@
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A264" s="7">
+      <c r="A264" s="1">
         <v>46186</v>
       </c>
       <c r="E264">
@@ -5646,7 +5945,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A265" s="7">
+      <c r="A265" s="1">
         <v>46193</v>
       </c>
       <c r="E265">
@@ -5663,7 +5962,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A266" s="7">
+      <c r="A266" s="1">
         <v>46194</v>
       </c>
       <c r="E266">
@@ -5680,7 +5979,7 @@
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A267" s="7">
+      <c r="A267" s="1">
         <v>46207</v>
       </c>
       <c r="E267">
@@ -5697,7 +5996,7 @@
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A268" s="7">
+      <c r="A268" s="1">
         <v>46207</v>
       </c>
       <c r="E268">
@@ -5714,19 +6013,6 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J134:J1048576 J1:J132">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/Cottage Rummy Data File.xlsx
+++ b/docs/Cottage Rummy Data File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomku\Dropbox\Personal\Cottage Rummy Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717F1250-6CDB-4136-B6CC-EE7420AB2EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D331F2C-847D-4E95-B653-12BA0C0091CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="-15720" windowWidth="27915" windowHeight="14385" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="945" yWindow="-14760" windowWidth="27915" windowHeight="14385" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="6" r:id="rId1"/>
@@ -475,7 +475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AKI268"/>
+  <dimension ref="A1:AKI270"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -5713,6 +5713,40 @@
         <v>435</v>
       </c>
     </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A269" s="5">
+        <v>46214</v>
+      </c>
+      <c r="E269">
+        <v>285</v>
+      </c>
+      <c r="F269">
+        <v>105</v>
+      </c>
+      <c r="G269">
+        <v>410</v>
+      </c>
+      <c r="H269">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A270" s="5">
+        <v>46214</v>
+      </c>
+      <c r="E270">
+        <v>85</v>
+      </c>
+      <c r="F270">
+        <v>240</v>
+      </c>
+      <c r="G270">
+        <v>245</v>
+      </c>
+      <c r="H270">
+        <v>335</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="J134:J1048576 J1:J132">
     <cfRule type="colorScale" priority="21">

--- a/docs/Cottage Rummy Data File.xlsx
+++ b/docs/Cottage Rummy Data File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomku\Dropbox\Personal\Cottage Rummy Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D331F2C-847D-4E95-B653-12BA0C0091CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C31678-76A9-4E3C-B786-842C6F98CC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="945" yWindow="-14760" windowWidth="27915" windowHeight="14385" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="945" yWindow="-14385" windowWidth="27915" windowHeight="14385" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="6" r:id="rId1"/>
@@ -475,7 +475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AKI270"/>
+  <dimension ref="A1:AKI271"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -5747,6 +5747,23 @@
         <v>335</v>
       </c>
     </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A271" s="5">
+        <v>46220</v>
+      </c>
+      <c r="C271">
+        <v>40</v>
+      </c>
+      <c r="D271">
+        <v>370</v>
+      </c>
+      <c r="G271">
+        <v>320</v>
+      </c>
+      <c r="H271">
+        <v>175</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="J134:J1048576 J1:J132">
     <cfRule type="colorScale" priority="21">
